--- a/artfynd/A 40179-2023 artfynd.xlsx
+++ b/artfynd/A 40179-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40179-2023 artfynd.xlsx
+++ b/artfynd/A 40179-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112065913</v>
       </c>
       <c r="B2" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,19 +695,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långflon (Långflon), Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -781,12 +776,7 @@
         <v>112065865</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,14 +805,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långflon (Långflon), Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>469609</v>
       </c>
       <c r="R3" t="n">
-        <v>7039805</v>
+        <v>7039806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,53 +871,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112065861</v>
+        <v>112370026</v>
       </c>
       <c r="B4" t="n">
-        <v>90305</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469608</v>
+        <v>469718</v>
       </c>
       <c r="R4" t="n">
-        <v>7039809</v>
+        <v>7039993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +936,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en sandbank nedanför tallskog. Mager mark.</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,19 +950,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -995,12 +971,7 @@
         <v>112370019</v>
       </c>
       <c r="B5" t="n">
-        <v>56511</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,15 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112370026</v>
+        <v>112065861</v>
       </c>
       <c r="B6" t="n">
-        <v>90906</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1085,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>256703</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>nybodarna Österulvsås, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469718</v>
+        <v>469608</v>
       </c>
       <c r="R6" t="n">
-        <v>7039994</v>
+        <v>7039809</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1142,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På en sandbank nedanför tallskog. Mager mark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,18 +1161,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 40179-2023 artfynd.xlsx
+++ b/artfynd/A 40179-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112065913</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112065865</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112065861</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>